--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/biobio.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/biobio.xlsx
@@ -623,7 +623,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1058,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1123,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1493,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1680,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1745,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +1993,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2180,11 @@
           <t>77.350.188-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2367,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2798,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3107,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4026,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4091,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4461,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4526,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4591,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4717,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4904,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5030,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5278,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6807,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +6872,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +6998,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7490,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +7982,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8169,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8478,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8726,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8791,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +8978,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +9897,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10023,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10088,11 @@
           <t>77.350.188-2</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10153,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10462,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10527,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10592,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10657,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +10905,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11092,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11157,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11283,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11348,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11535,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12027,11 @@
           <t>77.350.188-2</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12153,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12218,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12283,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12348,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12535,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12783,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +12970,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13218,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13466,11 @@
           <t>77.809.859-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +13836,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +13962,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14088,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14214,11 @@
           <t>76.193.188-1</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14279,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14405,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +14897,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15023,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15088,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15214,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15401,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15527,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15592,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +15901,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16271,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16641,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +16889,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +16954,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17019,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17389,11 @@
           <t>77.814.343-7</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +17637,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +17702,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +17767,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +17832,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +17897,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18023,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18149,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18214,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +18523,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +18649,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19385,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +19572,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +19759,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +19824,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +19889,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +19954,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20019,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20084,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20210,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20275,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20340,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20405,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +20470,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +20657,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +20783,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +20848,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +20913,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21222,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21348,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21413,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +21905,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22092,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22279,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22405,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +22531,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +22596,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +22661,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +22848,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +22913,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23222,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23287,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23352,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +23600,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +23726,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +23791,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +23856,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +23982,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24047,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24173,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24299,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +24486,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +24551,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +24616,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +24803,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +24929,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +24994,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +25303,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +25368,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +25494,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +25803,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +25868,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +25933,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +25998,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +26368,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +26433,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +26620,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +26807,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +26872,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27120,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27185,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +27372,11 @@
           <t>77.103.803-4</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +27925,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +28539,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +28848,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +28913,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +29222,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +29348,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +29474,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +29539,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +29665,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +29730,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30039,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +30104,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +30230,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +30295,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +30482,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +30913,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +30978,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31043,11 @@
           <t>77.601.843-0</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +31352,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +31417,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +31482,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +31547,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +31673,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +31738,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +31864,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +32051,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +32116,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +32425,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +32490,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +32616,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +32803,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +32868,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +33177,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +33303,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +33429,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +33738,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +34413,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +34539,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33990,7 +34726,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34234,7 +34974,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +35039,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34356,7 +35104,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +35169,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +35295,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +35543,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34966,7 +35730,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35149,7 +35917,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +35982,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +36047,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +36478,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35759,7 +36543,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35820,7 +36608,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35942,7 +36734,11 @@
           <t>77.601.843-0</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36064,7 +36860,11 @@
           <t>77.601.843-0</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36186,7 +36986,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36552,7 +37356,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36613,7 +37421,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37223,7 +38035,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37467,7 +38283,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37772,7 +38592,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37894,7 +38718,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37955,7 +38783,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38382,7 +39214,11 @@
           <t>77.601.843-0</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38504,7 +39340,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38565,7 +39405,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38626,7 +39470,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38748,7 +39596,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38809,7 +39661,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38870,7 +39726,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38931,7 +39791,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38992,7 +39856,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39541,7 +40409,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39602,7 +40474,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39846,7 +40722,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39968,7 +40848,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40090,7 +40974,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40273,7 +41161,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40334,7 +41226,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40517,7 +41413,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/biobio.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/biobio.xlsx
@@ -4217,7 +4217,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10218,7 +10222,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10279,7 +10287,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10401,7 +10413,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11844,7 +11860,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23478,7 +23498,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27311,7 +27335,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41100,7 +41128,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/biobio.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/biobio.xlsx
@@ -42661,7 +42661,7 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F677" t="inlineStr">
